--- a/data/Mar/17-03-2026/NGAY 17-3.xlsx
+++ b/data/Mar/17-03-2026/NGAY 17-3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\17-03-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\17-03-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CD379C-B1BC-4980-82BB-52E4D1FED26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D494AE9-9F7A-4711-9D71-EDA561B93F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6EAF8504-9B99-4CC8-A026-1F30ACB00849}"/>
   </bookViews>
@@ -979,11 +979,11 @@
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I6" s="2">
         <f>-H6</f>
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="J6" t="s">
         <v>54</v>
@@ -1711,11 +1711,11 @@
       </c>
       <c r="H26" s="3">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="I26" s="3">
         <f>SUBTOTAL(9,I3:I24)</f>
-        <v>12300</v>
+        <v>12295</v>
       </c>
       <c r="J26" s="3">
         <f t="shared" si="1"/>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="P30">
         <f>L35</f>
-        <v>3510</v>
+        <v>3466</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="C31" s="14">
         <f>-SUMIFS(H$3:H$111,$B$3:$B$111,$A29,$L$3:$L$111,$A30)</f>
-        <v>-630</v>
+        <v>-635</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31">
@@ -1872,6 +1872,9 @@
       <c r="K32" t="s">
         <v>28</v>
       </c>
+      <c r="L32">
+        <v>-44</v>
+      </c>
       <c r="O32" t="s">
         <v>107</v>
       </c>
@@ -1886,7 +1889,7 @@
       </c>
       <c r="C33" s="12">
         <f>SUBTOTAL(9,C30:C32)</f>
-        <v>12300</v>
+        <v>12295</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33">
@@ -1918,7 +1921,7 @@
       </c>
       <c r="P34">
         <f>-C37</f>
-        <v>-12300</v>
+        <v>-12295</v>
       </c>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.25">
@@ -1929,7 +1932,7 @@
       <c r="D35" s="10"/>
       <c r="L35" s="9">
         <f>SUBTOTAL(9,L30:L34)</f>
-        <v>3510</v>
+        <v>3466</v>
       </c>
       <c r="M35" s="9">
         <f>M30</f>
@@ -1940,7 +1943,7 @@
       </c>
       <c r="P35" s="4">
         <f>SUBTOTAL(9,P30:P34)</f>
-        <v>154</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
@@ -1949,7 +1952,7 @@
       </c>
       <c r="C37" s="11">
         <f>C33+C34+C35</f>
-        <v>12300</v>
+        <v>12295</v>
       </c>
       <c r="D37" s="11"/>
       <c r="E37" s="3" t="s">
